--- a/genai_activity_guidance_table.xlsx
+++ b/genai_activity_guidance_table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gla-my.sharepoint.com/personal/helena_paterson_glasgow_ac_uk/Documents/Documents/assessmentai/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2062" documentId="8_{29B8CF80-18B1-42DD-994F-A015760602C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6CE34B5D-DE33-4D2D-8488-71FE8115F169}"/>
+  <xr:revisionPtr revIDLastSave="2068" documentId="8_{29B8CF80-18B1-42DD-994F-A015760602C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9C23C29A-72D9-4200-A647-A84D754E677A}"/>
   <bookViews>
-    <workbookView xWindow="11200" yWindow="500" windowWidth="28800" windowHeight="15560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AI statement master table" sheetId="1" r:id="rId1"/>
@@ -1551,9 +1551,6 @@
     <t>new section-BM made minor corrections; check against: Technology-assisted data collection and transformation. In column D, I wasn't sure what "silent" meant in this context.  I'm also not sure I understand this clause: rather than as one input to your own judgement. BM added suggested skills category and asessment but should be checked; changed title to Data Processing</t>
   </si>
   <si>
-    <t>Translating written work from another language into English.  Students who are not native English speakers will often need to translate their thoughts from their primary language to English. The gold standard is to write the text in English from the start but where this creates challenges that compromise demonstration of learning, translation might be necessary. Support is available through English as a second language support, and feedback from staff or peers.</t>
-  </si>
-  <si>
     <t>GenAI offers sophisticated enhancement of translation software, and this is an expanding field that has significant future implications for communication across language barriers. Use GenAI-powered translation software to assit with translation of original work that you produce in another language to English (unless the testing of English Language is an ILO). Note that the nuance of an intended communication is likely to be lost or changed during any AI-assisted translation process so output should be carefully edited and refined. You can use it to help you to understand where you are making common mistakes in your use of English, to help to improve your writing in the future.  Good practice means using GenAI to help you to express your ideas more clearly but it should not be used to replace your own writing.</t>
   </si>
   <si>
@@ -1590,24 +1587,6 @@
     <t>Using GenAI for translation without knowing enough English to intepret meanings risks mispresentation of your ideas, or altering credit given via in-text citations. Translation should not be used as a replacement of learning to clearly communicate in English.  Failing to critically check outputs also risks miscommunicating field-specific terminology or using inappropriate terminology for your discipline. Over-reliance on GenAI limits your opportunity for practicing and improving communication in English, as well as confidence in the use of scientific and technical English.</t>
   </si>
   <si>
-    <t xml:space="preserve">Data analyses report, Research project, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Proposal, Research project, Group work, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data analyses report, Practical skills, Research project, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data analyses report, Presentation, Proposal, Research project, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data analyses report, Presentation, Practical skills, Proposal, Research project, </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data analyses report, Presentation, Research project, </t>
-  </si>
-  <si>
     <t>Reflection, Problem centred</t>
   </si>
   <si>
@@ -1617,12 +1596,6 @@
     <t xml:space="preserve">Essay or similar, Presentation, Proposal, Research project, </t>
   </si>
   <si>
-    <t>Essay or similar, Data analyses report, Presentation, Proposal, Research project, Reflection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data analyses report, Essay or similar, Presentation, Proposal, Research project, </t>
-  </si>
-  <si>
     <t>Essay or similar, Presentation, Proposal, Research project, Data analysis report</t>
   </si>
   <si>
@@ -1632,27 +1605,12 @@
     <t>Peer Review</t>
   </si>
   <si>
-    <t xml:space="preserve">Data analyses report, Essay or similar, Presentation, Reflection, Exam, Proposal, Research project, </t>
-  </si>
-  <si>
-    <t>Proposal, Research project, Group work, Essay or similar, Data analyses report, Practical Skills, Reflection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data analyses report, Essay or similar, Presentation, Reflection, Proposal, Research project, Group work, </t>
-  </si>
-  <si>
     <t>Reflection,</t>
   </si>
   <si>
     <t>Preparing for Oral Presentations</t>
   </si>
   <si>
-    <t>Data analyses report,  Practical skills, Presentation, Proposal, Research project, Problem centred</t>
-  </si>
-  <si>
-    <t>Data analyses report, Practical skills, Research project, Problem centred</t>
-  </si>
-  <si>
     <t>Reflection, Presentation, Proposal, Groupwork, Research project</t>
   </si>
   <si>
@@ -1684,6 +1642,48 @@
   </si>
   <si>
     <t>Skills-specific assessment</t>
+  </si>
+  <si>
+    <t>Essay or similar, Data analysis report, Presentation, Proposal, Research project, Reflection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Research project, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Practical skills, Research project, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Presentation, Proposal, Research project, </t>
+  </si>
+  <si>
+    <t>Data analysis report,  Practical skills, Presentation, Proposal, Research project, Problem centred</t>
+  </si>
+  <si>
+    <t>Data analysis report, Practical skills, Research project, Problem centred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Presentation, Practical skills, Proposal, Research project, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Essay or similar, Presentation, Reflection, Exam, Proposal, Research project, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Essay or similar, Presentation, Proposal, Research project, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Presentation, Research project, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Proposal, Research project, Groupwork, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data analysis report, Essay or similar, Presentation, Reflection, Proposal, Research project, Groupwork, </t>
+  </si>
+  <si>
+    <t>Proposal, Research project, Groupwork, Essay or similar, Data analysis report, Practical skills, Reflection</t>
+  </si>
+  <si>
+    <t>Translating written work from another language into English.  Students who are are not Enghlish first language speakers will often need to translate their thoughts from their primary language to English. The gold standard is to write the text in English from the start but where this creates challenges that compromise demonstration of learning, translation might be necessary. Support is available through English as a second language support, and feedback from staff or peers.</t>
   </si>
 </sst>
 </file>
@@ -4001,20 +4001,20 @@
     <tabColor theme="6"/>
   </sheetPr>
   <dimension ref="A1:I34"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="63.1640625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="63.109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="29.77734375" style="2" customWidth="1"/>
     <col min="2" max="2" width="50" style="6" customWidth="1"/>
     <col min="3" max="3" width="49.33203125" style="6" customWidth="1"/>
     <col min="4" max="4" width="49.33203125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="10" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" style="32" customWidth="1"/>
-    <col min="7" max="7" width="28.5" style="10" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" style="32" customWidth="1"/>
-    <col min="10" max="16384" width="63.1640625" style="6"/>
+    <col min="5" max="5" width="20.44140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" style="32" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="26.77734375" style="32" customWidth="1"/>
+    <col min="10" max="16384" width="63.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>350</v>
       </c>
@@ -4031,10 +4031,10 @@
         <v>0</v>
       </c>
       <c r="F1" s="31" t="s">
-        <v>486</v>
+        <v>472</v>
       </c>
       <c r="G1" s="26" t="s">
-        <v>487</v>
+        <v>473</v>
       </c>
       <c r="H1" s="40" t="s">
         <v>370</v>
@@ -4043,7 +4043,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="143" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="142.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>39</v>
       </c>
@@ -4054,13 +4054,13 @@
         <v>411</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>481</v>
+        <v>467</v>
       </c>
       <c r="E2" s="10" t="s">
         <v>12</v>
       </c>
       <c r="F2" s="32" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G2" s="14" t="s">
         <v>320</v>
@@ -4072,7 +4072,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="173" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="172.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="37" t="s">
         <v>3</v>
       </c>
@@ -4089,7 +4089,7 @@
         <v>4</v>
       </c>
       <c r="F3" s="61" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>306</v>
@@ -4101,7 +4101,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="161" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="160.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>73</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>64</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="G4" s="14" t="s">
         <v>332</v>
@@ -4130,7 +4130,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="83" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="82.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="12" t="s">
         <v>31</v>
       </c>
@@ -4147,7 +4147,7 @@
         <v>29</v>
       </c>
       <c r="F5" s="32" t="s">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="G5" s="14" t="s">
         <v>316</v>
@@ -4159,7 +4159,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>51</v>
       </c>
@@ -4176,7 +4176,7 @@
         <v>29</v>
       </c>
       <c r="F6" s="32" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="G6" s="15" t="s">
         <v>324</v>
@@ -4188,7 +4188,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="126" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>63</v>
       </c>
@@ -4205,7 +4205,7 @@
         <v>64</v>
       </c>
       <c r="F7" s="32" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="G7" s="14" t="s">
         <v>331</v>
@@ -4217,7 +4217,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="213" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="213" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>441</v>
       </c>
@@ -4228,13 +4228,13 @@
         <v>415</v>
       </c>
       <c r="D8" s="62" t="s">
-        <v>479</v>
+        <v>465</v>
       </c>
       <c r="E8" s="10" t="s">
         <v>64</v>
       </c>
       <c r="F8" s="32" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="G8" s="14" t="s">
         <v>416</v>
@@ -4246,7 +4246,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="112" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="112.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>325</v>
       </c>
@@ -4263,7 +4263,7 @@
         <v>29</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G9" s="56" t="s">
         <v>326</v>
@@ -4275,7 +4275,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>28</v>
       </c>
@@ -4286,13 +4286,13 @@
         <v>396</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>480</v>
+        <v>466</v>
       </c>
       <c r="E10" s="10" t="s">
         <v>29</v>
       </c>
       <c r="F10" s="32" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="G10" s="14" t="s">
         <v>315</v>
@@ -4304,7 +4304,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="90" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
         <v>17</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>336</v>
       </c>
       <c r="F11" s="32" t="s">
-        <v>460</v>
+        <v>480</v>
       </c>
       <c r="G11" s="14" t="s">
         <v>311</v>
@@ -4333,7 +4333,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
         <v>11</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>12</v>
       </c>
       <c r="F12" s="32" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="G12" s="14" t="s">
         <v>309</v>
@@ -4362,7 +4362,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="137" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="136.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>182</v>
       </c>
@@ -4379,7 +4379,7 @@
         <v>29</v>
       </c>
       <c r="F13" s="32" t="s">
-        <v>471</v>
+        <v>486</v>
       </c>
       <c r="G13" s="14" t="s">
         <v>317</v>
@@ -4391,7 +4391,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="106" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="106.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>35</v>
       </c>
@@ -4408,7 +4408,7 @@
         <v>4</v>
       </c>
       <c r="F14" s="32" t="s">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="G14" s="14" t="s">
         <v>318</v>
@@ -4420,7 +4420,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="96.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="96.45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="37" t="s">
         <v>19</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>336</v>
       </c>
       <c r="F15" s="32" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="G15" s="14" t="s">
         <v>312</v>
@@ -4449,7 +4449,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="178" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="178.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="37" t="s">
         <v>6</v>
       </c>
@@ -4460,13 +4460,13 @@
         <v>387</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>482</v>
+        <v>468</v>
       </c>
       <c r="E16" s="10" t="s">
         <v>7</v>
       </c>
       <c r="F16" s="32" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="G16" s="14" t="s">
         <v>307</v>
@@ -4478,7 +4478,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="114" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="37" t="s">
         <v>10</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>7</v>
       </c>
       <c r="F17" s="32" t="s">
-        <v>466</v>
+        <v>482</v>
       </c>
       <c r="G17" s="14" t="s">
         <v>308</v>
@@ -4507,7 +4507,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="125" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="124.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>130</v>
       </c>
@@ -4536,9 +4536,9 @@
         <v>418</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="97" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="97.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>170</v>
@@ -4553,7 +4553,7 @@
         <v>336</v>
       </c>
       <c r="F19" s="32" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="G19" s="14" t="s">
         <v>313</v>
@@ -4565,9 +4565,9 @@
         <v>388</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="160" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="160.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>116</v>
@@ -4594,7 +4594,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="117" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="117" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>69</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>336</v>
       </c>
       <c r="F21" s="32" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="G21" s="15" t="s">
         <v>334</v>
@@ -4623,7 +4623,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="100.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>71</v>
       </c>
@@ -4640,7 +4640,7 @@
         <v>336</v>
       </c>
       <c r="F22" s="32" t="s">
-        <v>463</v>
+        <v>456</v>
       </c>
       <c r="G22" s="14" t="s">
         <v>335</v>
@@ -4652,7 +4652,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="130" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>41</v>
       </c>
@@ -4669,7 +4669,7 @@
         <v>12</v>
       </c>
       <c r="F23" s="32" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="G23" s="14" t="s">
         <v>321</v>
@@ -4681,7 +4681,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="103" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="103.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>24</v>
       </c>
@@ -4692,7 +4692,7 @@
         <v>422</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="E24" s="10" t="s">
         <v>12</v>
@@ -4710,7 +4710,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="142" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="142.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>56</v>
       </c>
@@ -4721,13 +4721,13 @@
         <v>424</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>484</v>
+        <v>470</v>
       </c>
       <c r="E25" s="10" t="s">
         <v>336</v>
       </c>
       <c r="F25" s="32" t="s">
-        <v>461</v>
+        <v>483</v>
       </c>
       <c r="G25" s="14" t="s">
         <v>327</v>
@@ -4739,7 +4739,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="104" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="103.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>37</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="116" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="115.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>59</v>
       </c>
@@ -4785,7 +4785,7 @@
         <v>45</v>
       </c>
       <c r="F27" s="32" t="s">
-        <v>464</v>
+        <v>457</v>
       </c>
       <c r="G27" s="14" t="s">
         <v>329</v>
@@ -4795,7 +4795,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" ht="170.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="170.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>48</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>155</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>485</v>
+        <v>471</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>157</v>
@@ -4812,19 +4812,19 @@
         <v>4</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>478</v>
+        <v>464</v>
       </c>
       <c r="G28" s="14" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H28" s="41" t="s">
         <v>373</v>
       </c>
       <c r="I28" s="6" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="134" customHeight="1" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="133.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>66</v>
       </c>
@@ -4841,7 +4841,7 @@
         <v>64</v>
       </c>
       <c r="F29" s="32" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="G29" s="14" t="s">
         <v>333</v>
@@ -4851,7 +4851,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" ht="110" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="109.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="37" t="s">
         <v>437</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>12</v>
       </c>
       <c r="F30" s="32" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="G30" s="14" t="s">
         <v>310</v>
@@ -4880,7 +4880,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="133" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="133.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>61</v>
       </c>
@@ -4909,36 +4909,36 @@
         <v>429</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="193" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" ht="193.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>440</v>
       </c>
       <c r="B32" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="C32" s="59" t="s">
         <v>443</v>
       </c>
-      <c r="C32" s="59" t="s">
-        <v>444</v>
-      </c>
       <c r="D32" s="19" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E32" s="21" t="s">
         <v>45</v>
       </c>
       <c r="F32" s="32" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="G32" s="22" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H32" s="42" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="I32" s="6" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="153" customHeight="1" x14ac:dyDescent="0.2">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="153" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="17" t="s">
         <v>431</v>
       </c>
@@ -4961,39 +4961,39 @@
         <v>435</v>
       </c>
       <c r="H33" s="42" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I33" s="6" t="s">
         <v>436</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="166" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="166.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="17" t="s">
+        <v>448</v>
+      </c>
+      <c r="B34" s="58" t="s">
+        <v>451</v>
+      </c>
+      <c r="C34" s="58" t="s">
         <v>449</v>
       </c>
-      <c r="B34" s="58" t="s">
+      <c r="D34" s="58" t="s">
         <v>452</v>
-      </c>
-      <c r="C34" s="58" t="s">
-        <v>450</v>
-      </c>
-      <c r="D34" s="58" t="s">
-        <v>453</v>
       </c>
       <c r="E34" s="21" t="s">
         <v>4</v>
       </c>
       <c r="F34" s="60" t="s">
-        <v>477</v>
+        <v>463</v>
       </c>
       <c r="G34" s="22" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H34" s="42" t="s">
         <v>378</v>
       </c>
       <c r="I34" s="57" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -5011,20 +5011,20 @@
     <tabColor theme="6"/>
   </sheetPr>
   <dimension ref="A1:I31"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="63.1640625" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="63.109375" defaultRowHeight="24" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29.83203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="29.77734375" style="2" customWidth="1"/>
     <col min="2" max="2" width="50" style="6" customWidth="1"/>
     <col min="3" max="3" width="49.33203125" style="6" customWidth="1"/>
     <col min="4" max="4" width="49.33203125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="10" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" style="32" customWidth="1"/>
-    <col min="7" max="7" width="28.5" style="10" customWidth="1"/>
-    <col min="8" max="8" width="26.83203125" style="32" customWidth="1"/>
-    <col min="10" max="16384" width="63.1640625" style="6"/>
+    <col min="5" max="5" width="20.44140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" style="32" customWidth="1"/>
+    <col min="7" max="7" width="28.44140625" style="10" customWidth="1"/>
+    <col min="8" max="8" width="26.77734375" style="32" customWidth="1"/>
+    <col min="10" max="16384" width="63.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" s="27" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>350</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="143" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="142.94999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="37" t="s">
         <v>3</v>
       </c>
@@ -5082,7 +5082,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="173" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="172.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="37" t="s">
         <v>6</v>
       </c>
@@ -5111,7 +5111,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="108" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="37" t="s">
         <v>10</v>
       </c>
@@ -5140,7 +5140,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="83" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="82.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
         <v>17</v>
       </c>
@@ -5169,7 +5169,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="85" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="85.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>28</v>
       </c>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="91" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" ht="91.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="12" t="s">
         <v>31</v>
       </c>
@@ -5223,7 +5223,7 @@
       </c>
       <c r="I7" s="6"/>
     </row>
-    <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>182</v>
       </c>
@@ -5250,7 +5250,7 @@
       </c>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
         <v>51</v>
       </c>
@@ -5277,7 +5277,7 @@
       </c>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>325</v>
       </c>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>73</v>
       </c>
@@ -5331,7 +5331,7 @@
       </c>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>63</v>
       </c>
@@ -5358,7 +5358,7 @@
       </c>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>66</v>
       </c>
@@ -5385,7 +5385,7 @@
       </c>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
         <v>21</v>
       </c>
@@ -5412,7 +5412,7 @@
       </c>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>56</v>
       </c>
@@ -5439,7 +5439,7 @@
       </c>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>41</v>
       </c>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="37" t="s">
         <v>19</v>
       </c>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="37" t="s">
         <v>11</v>
       </c>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="37" t="s">
         <v>15</v>
       </c>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="I19" s="6"/>
     </row>
-    <row r="20" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>61</v>
       </c>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="I20" s="6"/>
     </row>
-    <row r="21" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>39</v>
       </c>
@@ -5601,7 +5601,7 @@
       </c>
       <c r="I21" s="6"/>
     </row>
-    <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>130</v>
       </c>
@@ -5628,7 +5628,7 @@
       </c>
       <c r="I22" s="6"/>
     </row>
-    <row r="23" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>59</v>
       </c>
@@ -5655,7 +5655,7 @@
       </c>
       <c r="I23" s="6"/>
     </row>
-    <row r="24" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>44</v>
       </c>
@@ -5682,7 +5682,7 @@
       </c>
       <c r="I24" s="6"/>
     </row>
-    <row r="25" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>24</v>
       </c>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="I25" s="6"/>
     </row>
-    <row r="26" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>37</v>
       </c>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="I26" s="6"/>
     </row>
-    <row r="27" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>48</v>
       </c>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="I27" s="6"/>
     </row>
-    <row r="28" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>35</v>
       </c>
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I28" s="6"/>
     </row>
-    <row r="29" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>69</v>
       </c>
@@ -5817,7 +5817,7 @@
       </c>
       <c r="I29" s="6"/>
     </row>
-    <row r="30" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>71</v>
       </c>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="I30" s="6"/>
     </row>
-    <row r="31" spans="1:9" ht="146.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" ht="146.55000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="17" t="s">
         <v>384</v>
       </c>
@@ -5873,14 +5873,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{302D6E88-2826-4AD3-BDD3-65D86D8AD191}">
   <dimension ref="A1:S30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="61.1640625" customWidth="1"/>
+    <col min="1" max="1" width="61.109375" customWidth="1"/>
     <col min="2" max="2" width="65" customWidth="1"/>
-    <col min="3" max="3" width="75.5" style="36" customWidth="1"/>
+    <col min="3" max="3" width="75.44140625" style="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A1" s="29" t="s">
         <v>253</v>
       </c>
@@ -5925,7 +5925,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A2" s="30" t="s">
         <v>3</v>
       </c>
@@ -5969,7 +5969,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
         <v>6</v>
       </c>
@@ -6004,7 +6004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A4" s="30" t="s">
         <v>10</v>
       </c>
@@ -6036,7 +6036,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A5" s="30" t="s">
         <v>11</v>
       </c>
@@ -6080,7 +6080,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A6" s="30" t="s">
         <v>15</v>
       </c>
@@ -6128,7 +6128,7 @@
         <v xml:space="preserve">Online quiz, </v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A7" s="30" t="s">
         <v>17</v>
       </c>
@@ -6164,7 +6164,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A8" s="30" t="s">
         <v>19</v>
       </c>
@@ -6200,7 +6200,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A9" s="30" t="s">
         <v>21</v>
       </c>
@@ -6216,7 +6216,7 @@
         <v xml:space="preserve">Peer review, </v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A10" s="30" t="s">
         <v>24</v>
       </c>
@@ -6232,7 +6232,7 @@
         <v xml:space="preserve">Proposal, </v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A11" s="30" t="s">
         <v>28</v>
       </c>
@@ -6256,7 +6256,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A12" s="30" t="s">
         <v>31</v>
       </c>
@@ -6280,7 +6280,7 @@
         <v xml:space="preserve">Group work, </v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="30" t="s">
         <v>182</v>
       </c>
@@ -6304,7 +6304,7 @@
         <v xml:space="preserve">Group work, </v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A14" s="30" t="s">
         <v>35</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v xml:space="preserve">Group work, </v>
       </c>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A15" s="30" t="s">
         <v>37</v>
       </c>
@@ -6364,7 +6364,7 @@
         <v xml:space="preserve">Essay or similar, </v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A16" s="30" t="s">
         <v>39</v>
       </c>
@@ -6392,7 +6392,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="30" t="s">
         <v>41</v>
       </c>
@@ -6412,7 +6412,7 @@
         <v xml:space="preserve">Peer review, </v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="30" t="s">
         <v>44</v>
       </c>
@@ -6428,7 +6428,7 @@
         <v xml:space="preserve">Presentation, </v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="30" t="s">
         <v>48</v>
       </c>
@@ -6452,7 +6452,7 @@
         <v xml:space="preserve">Online quiz, </v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="30" t="s">
         <v>51</v>
       </c>
@@ -6476,7 +6476,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="30" t="s">
         <v>54</v>
       </c>
@@ -6500,7 +6500,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="30" t="s">
         <v>56</v>
       </c>
@@ -6524,7 +6524,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="30" t="s">
         <v>130</v>
       </c>
@@ -6548,7 +6548,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="30" t="s">
         <v>59</v>
       </c>
@@ -6576,7 +6576,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="30" t="s">
         <v>61</v>
       </c>
@@ -6596,7 +6596,7 @@
         <v xml:space="preserve">Proposal, </v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="30" t="s">
         <v>63</v>
       </c>
@@ -6624,7 +6624,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="30" t="s">
         <v>73</v>
       </c>
@@ -6644,7 +6644,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="30" t="s">
         <v>66</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v xml:space="preserve">Dissertation, </v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="30" t="s">
         <v>69</v>
       </c>
@@ -6692,7 +6692,7 @@
         <v xml:space="preserve">Online quiz, </v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="30" t="s">
         <v>71</v>
       </c>
@@ -6727,18 +6727,18 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:G108"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="69.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="69.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="24.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="81.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="81.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="81" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="81.1640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="69.5" style="28"/>
+    <col min="6" max="6" width="21.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="69.44140625" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
@@ -6761,7 +6761,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>264</v>
       </c>
@@ -6784,7 +6784,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>257</v>
       </c>
@@ -6807,7 +6807,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>236</v>
       </c>
@@ -6830,7 +6830,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>273</v>
       </c>
@@ -6853,7 +6853,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>265</v>
       </c>
@@ -6876,7 +6876,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>266</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>272</v>
       </c>
@@ -6922,7 +6922,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>259</v>
       </c>
@@ -6945,7 +6945,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>264</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>257</v>
       </c>
@@ -6991,7 +6991,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>236</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>272</v>
       </c>
@@ -7037,7 +7037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="128" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>259</v>
       </c>
@@ -7060,7 +7060,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>264</v>
       </c>
@@ -7083,7 +7083,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>257</v>
       </c>
@@ -7106,7 +7106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>236</v>
       </c>
@@ -7129,7 +7129,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>272</v>
       </c>
@@ -7152,7 +7152,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>259</v>
       </c>
@@ -7175,7 +7175,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>264</v>
       </c>
@@ -7198,7 +7198,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>257</v>
       </c>
@@ -7221,7 +7221,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>236</v>
       </c>
@@ -7244,7 +7244,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>273</v>
       </c>
@@ -7267,7 +7267,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>256</v>
       </c>
@@ -7290,7 +7290,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>266</v>
       </c>
@@ -7313,7 +7313,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>272</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>259</v>
       </c>
@@ -7359,7 +7359,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>264</v>
       </c>
@@ -7382,7 +7382,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>257</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>236</v>
       </c>
@@ -7428,7 +7428,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>273</v>
       </c>
@@ -7451,7 +7451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>256</v>
       </c>
@@ -7474,7 +7474,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>266</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>272</v>
       </c>
@@ -7520,7 +7520,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>259</v>
       </c>
@@ -7543,7 +7543,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>264</v>
       </c>
@@ -7566,7 +7566,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>257</v>
       </c>
@@ -7589,7 +7589,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>236</v>
       </c>
@@ -7612,7 +7612,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>265</v>
       </c>
@@ -7635,7 +7635,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>272</v>
       </c>
@@ -7658,7 +7658,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>259</v>
       </c>
@@ -7681,7 +7681,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>264</v>
       </c>
@@ -7704,7 +7704,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>257</v>
       </c>
@@ -7727,7 +7727,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>236</v>
       </c>
@@ -7750,7 +7750,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>266</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>272</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>259</v>
       </c>
@@ -7819,7 +7819,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>266</v>
       </c>
@@ -7842,7 +7842,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>272</v>
       </c>
@@ -7865,7 +7865,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>264</v>
       </c>
@@ -7888,7 +7888,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>265</v>
       </c>
@@ -7911,7 +7911,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="48" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>259</v>
       </c>
@@ -7934,7 +7934,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>272</v>
       </c>
@@ -7957,7 +7957,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>259</v>
       </c>
@@ -7980,7 +7980,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>293</v>
       </c>
@@ -8003,7 +8003,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>272</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>259</v>
       </c>
@@ -8049,7 +8049,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>293</v>
       </c>
@@ -8072,7 +8072,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>264</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>257</v>
       </c>
@@ -8118,7 +8118,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>236</v>
       </c>
@@ -8141,7 +8141,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>273</v>
       </c>
@@ -8164,7 +8164,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>266</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>272</v>
       </c>
@@ -8210,7 +8210,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>259</v>
       </c>
@@ -8233,7 +8233,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>293</v>
       </c>
@@ -8256,7 +8256,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>257</v>
       </c>
@@ -8279,7 +8279,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>257</v>
       </c>
@@ -8302,7 +8302,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>236</v>
       </c>
@@ -8325,7 +8325,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>272</v>
       </c>
@@ -8348,7 +8348,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>259</v>
       </c>
@@ -8371,7 +8371,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>273</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>266</v>
       </c>
@@ -8417,7 +8417,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>236</v>
       </c>
@@ -8440,7 +8440,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>256</v>
       </c>
@@ -8463,7 +8463,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>265</v>
       </c>
@@ -8486,7 +8486,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>264</v>
       </c>
@@ -8509,7 +8509,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>265</v>
       </c>
@@ -8532,7 +8532,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>259</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>264</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>265</v>
       </c>
@@ -8601,7 +8601,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>259</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>264</v>
       </c>
@@ -8647,7 +8647,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>236</v>
       </c>
@@ -8670,7 +8670,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>259</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>236</v>
       </c>
@@ -8716,7 +8716,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>272</v>
       </c>
@@ -8739,7 +8739,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="96" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>259</v>
       </c>
@@ -8762,7 +8762,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>257</v>
       </c>
@@ -8785,7 +8785,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>236</v>
       </c>
@@ -8808,7 +8808,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>272</v>
       </c>
@@ -8831,7 +8831,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>259</v>
       </c>
@@ -8854,7 +8854,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>236</v>
       </c>
@@ -8877,7 +8877,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>272</v>
       </c>
@@ -8900,7 +8900,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>264</v>
       </c>
@@ -8923,7 +8923,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>236</v>
       </c>
@@ -8946,7 +8946,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>272</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>259</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>264</v>
       </c>
@@ -9015,7 +9015,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>259</v>
       </c>
@@ -9038,7 +9038,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>264</v>
       </c>
@@ -9061,7 +9061,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>265</v>
       </c>
@@ -9084,7 +9084,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>259</v>
       </c>
@@ -9107,7 +9107,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>273</v>
       </c>
@@ -9130,7 +9130,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>254</v>
       </c>
@@ -9153,7 +9153,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>256</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="64" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>254</v>
       </c>
@@ -9199,7 +9199,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="112" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>264</v>
       </c>
@@ -9228,19 +9228,19 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:G120"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="31.6640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="81.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="81.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="21.5" style="28" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="81.1640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="28"/>
+    <col min="2" max="2" width="52.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="81.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.44140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="81.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>295</v>
       </c>
@@ -9263,7 +9263,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>252</v>
       </c>
@@ -9286,7 +9286,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="3" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>36</v>
       </c>
@@ -9309,7 +9309,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="128" hidden="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="129.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>189</v>
       </c>
@@ -9332,7 +9332,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="5" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>190</v>
       </c>
@@ -9355,7 +9355,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="6" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>191</v>
       </c>
@@ -9378,7 +9378,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="7" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>192</v>
       </c>
@@ -9401,7 +9401,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="8" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>193</v>
       </c>
@@ -9424,7 +9424,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="9" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>194</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="10" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>189</v>
       </c>
@@ -9493,7 +9493,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="12" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>190</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="13" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>191</v>
       </c>
@@ -9539,7 +9539,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="14" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>192</v>
       </c>
@@ -9562,7 +9562,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="15" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>193</v>
       </c>
@@ -9585,7 +9585,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="16" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>194</v>
       </c>
@@ -9608,7 +9608,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="17" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -9631,7 +9631,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="80" hidden="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="86.4" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>195</v>
       </c>
@@ -9654,7 +9654,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="19" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>196</v>
       </c>
@@ -9677,7 +9677,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="20" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>191</v>
       </c>
@@ -9700,7 +9700,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="21" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>197</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>198</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="80" hidden="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>189</v>
       </c>
@@ -9769,7 +9769,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="24" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>190</v>
       </c>
@@ -9792,7 +9792,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="25" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>191</v>
       </c>
@@ -9815,7 +9815,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="26" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>192</v>
       </c>
@@ -9838,7 +9838,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="27" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>193</v>
       </c>
@@ -9861,7 +9861,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="28" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>194</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="29" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -9907,7 +9907,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>189</v>
       </c>
@@ -9930,7 +9930,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="31" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>190</v>
       </c>
@@ -9953,7 +9953,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="32" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>191</v>
       </c>
@@ -9976,7 +9976,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="33" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>192</v>
       </c>
@@ -9999,7 +9999,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="34" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>193</v>
       </c>
@@ -10022,7 +10022,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>194</v>
       </c>
@@ -10045,7 +10045,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="36" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>36</v>
       </c>
@@ -10068,7 +10068,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="64" hidden="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>189</v>
       </c>
@@ -10091,7 +10091,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="38" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>190</v>
       </c>
@@ -10114,7 +10114,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="39" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>191</v>
       </c>
@@ -10137,7 +10137,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="40" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>192</v>
       </c>
@@ -10160,7 +10160,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="41" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>193</v>
       </c>
@@ -10183,7 +10183,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="42" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>194</v>
       </c>
@@ -10206,7 +10206,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="43" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>199</v>
       </c>
@@ -10229,7 +10229,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="44" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>200</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="45" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>201</v>
       </c>
@@ -10275,7 +10275,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="46" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>202</v>
       </c>
@@ -10298,7 +10298,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="47" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>192</v>
       </c>
@@ -10321,7 +10321,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="48" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>203</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="49" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>204</v>
       </c>
@@ -10367,7 +10367,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="50" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>205</v>
       </c>
@@ -10390,7 +10390,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="51" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>189</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="52" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>192</v>
       </c>
@@ -10436,7 +10436,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="53" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>206</v>
       </c>
@@ -10459,7 +10459,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="54" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>207</v>
       </c>
@@ -10482,7 +10482,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="55" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>208</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="56" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>209</v>
       </c>
@@ -10528,7 +10528,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="57" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>36</v>
       </c>
@@ -10551,7 +10551,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="96" hidden="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="100.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>189</v>
       </c>
@@ -10574,7 +10574,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="59" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>190</v>
       </c>
@@ -10597,7 +10597,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="60" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>191</v>
       </c>
@@ -10620,7 +10620,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="61" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>192</v>
       </c>
@@ -10643,7 +10643,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="62" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>193</v>
       </c>
@@ -10666,7 +10666,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>194</v>
       </c>
@@ -10689,7 +10689,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="64" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>36</v>
       </c>
@@ -10712,7 +10712,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="80" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="72" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>210</v>
       </c>
@@ -10735,7 +10735,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="66" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>211</v>
       </c>
@@ -10758,7 +10758,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="67" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>212</v>
       </c>
@@ -10781,7 +10781,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="68" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>213</v>
       </c>
@@ -10804,7 +10804,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="69" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>203</v>
       </c>
@@ -10827,7 +10827,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="70" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>189</v>
       </c>
@@ -10850,7 +10850,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="71" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>214</v>
       </c>
@@ -10873,7 +10873,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="72" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>215</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="73" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>216</v>
       </c>
@@ -10919,7 +10919,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="74" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>188</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="75" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>217</v>
       </c>
@@ -10965,7 +10965,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="76" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>218</v>
       </c>
@@ -10988,7 +10988,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="77" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>219</v>
       </c>
@@ -11011,7 +11011,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="78" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>208</v>
       </c>
@@ -11034,7 +11034,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="79" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>220</v>
       </c>
@@ -11057,7 +11057,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="80" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>221</v>
       </c>
@@ -11080,7 +11080,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="81" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>222</v>
       </c>
@@ -11103,7 +11103,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="82" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>223</v>
       </c>
@@ -11126,7 +11126,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="83" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>224</v>
       </c>
@@ -11149,7 +11149,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="84" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>204</v>
       </c>
@@ -11172,7 +11172,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="85" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>189</v>
       </c>
@@ -11195,7 +11195,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="86" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>225</v>
       </c>
@@ -11218,7 +11218,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="87" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>226</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="88" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>227</v>
       </c>
@@ -11264,7 +11264,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="89" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>228</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="90" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>206</v>
       </c>
@@ -11310,7 +11310,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="91" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>226</v>
       </c>
@@ -11333,7 +11333,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="92" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>229</v>
       </c>
@@ -11356,7 +11356,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="93" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>230</v>
       </c>
@@ -11379,7 +11379,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="94" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>192</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="95" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>231</v>
       </c>
@@ -11425,7 +11425,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="96" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>232</v>
       </c>
@@ -11448,7 +11448,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="97" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>233</v>
       </c>
@@ -11471,7 +11471,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="98" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>234</v>
       </c>
@@ -11494,7 +11494,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="99" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>235</v>
       </c>
@@ -11517,7 +11517,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="100" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>232</v>
       </c>
@@ -11540,7 +11540,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="101" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>236</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="102" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>237</v>
       </c>
@@ -11586,7 +11586,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="103" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>238</v>
       </c>
@@ -11609,7 +11609,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="104" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>226</v>
       </c>
@@ -11632,7 +11632,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="105" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>239</v>
       </c>
@@ -11655,7 +11655,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="106" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>240</v>
       </c>
@@ -11678,7 +11678,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="107" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>226</v>
       </c>
@@ -11701,7 +11701,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="108" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>223</v>
       </c>
@@ -11724,7 +11724,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="109" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>241</v>
       </c>
@@ -11747,7 +11747,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="110" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>242</v>
       </c>
@@ -11770,7 +11770,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="111" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>243</v>
       </c>
@@ -11793,7 +11793,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="112" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>244</v>
       </c>
@@ -11816,7 +11816,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="113" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>245</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="114" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>246</v>
       </c>
@@ -11862,7 +11862,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="115" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>247</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="116" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>248</v>
       </c>
@@ -11908,7 +11908,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="117" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>249</v>
       </c>
@@ -11931,7 +11931,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="118" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>250</v>
       </c>
@@ -11954,7 +11954,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="119" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" customFormat="1" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>251</v>
       </c>
@@ -11977,7 +11977,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="120" spans="1:7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A120" s="28"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -12001,19 +12001,19 @@
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:G136"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="77.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="81.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="81.1640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="28"/>
+    <col min="5" max="5" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="81.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>187</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
@@ -12059,7 +12059,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -12082,7 +12082,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>130</v>
       </c>
@@ -12105,7 +12105,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
@@ -12128,7 +12128,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>130</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>130</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -12197,7 +12197,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>59</v>
       </c>
@@ -12243,7 +12243,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
@@ -12266,7 +12266,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -12289,7 +12289,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -12335,7 +12335,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
@@ -12358,7 +12358,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -12381,7 +12381,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -12404,7 +12404,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -12427,7 +12427,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -12473,7 +12473,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -12496,7 +12496,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
@@ -12519,7 +12519,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -12542,7 +12542,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -12588,7 +12588,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -12611,7 +12611,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -12634,7 +12634,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -12657,7 +12657,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>19</v>
       </c>
@@ -12680,7 +12680,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>21</v>
       </c>
@@ -12703,7 +12703,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>21</v>
       </c>
@@ -12726,7 +12726,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>56</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>56</v>
       </c>
@@ -12772,7 +12772,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>56</v>
       </c>
@@ -12795,7 +12795,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>56</v>
       </c>
@@ -12818,7 +12818,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>69</v>
       </c>
@@ -12841,7 +12841,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>69</v>
       </c>
@@ -12864,7 +12864,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>69</v>
       </c>
@@ -12887,7 +12887,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>71</v>
       </c>
@@ -12910,7 +12910,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>71</v>
       </c>
@@ -12933,7 +12933,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>71</v>
       </c>
@@ -12956,7 +12956,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>63</v>
       </c>
@@ -12979,7 +12979,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>63</v>
       </c>
@@ -13002,7 +13002,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>63</v>
       </c>
@@ -13025,7 +13025,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>63</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>63</v>
       </c>
@@ -13071,7 +13071,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>66</v>
       </c>
@@ -13094,7 +13094,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>66</v>
       </c>
@@ -13117,7 +13117,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>66</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>66</v>
       </c>
@@ -13163,7 +13163,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
@@ -13186,7 +13186,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>73</v>
       </c>
@@ -13209,7 +13209,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>73</v>
       </c>
@@ -13232,7 +13232,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>6</v>
       </c>
@@ -13255,7 +13255,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>6</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -13301,7 +13301,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>6</v>
       </c>
@@ -13324,7 +13324,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>6</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>6</v>
       </c>
@@ -13370,7 +13370,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>10</v>
       </c>
@@ -13393,7 +13393,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>10</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
@@ -13439,7 +13439,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -13462,7 +13462,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>10</v>
       </c>
@@ -13485,7 +13485,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>10</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>28</v>
       </c>
@@ -13531,7 +13531,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>28</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>28</v>
       </c>
@@ -13577,7 +13577,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>28</v>
       </c>
@@ -13600,7 +13600,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>31</v>
       </c>
@@ -13623,7 +13623,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>31</v>
       </c>
@@ -13646,7 +13646,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>31</v>
       </c>
@@ -13669,7 +13669,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>31</v>
       </c>
@@ -13692,7 +13692,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>51</v>
       </c>
@@ -13715,7 +13715,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>51</v>
       </c>
@@ -13738,7 +13738,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>51</v>
       </c>
@@ -13761,7 +13761,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>51</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>325</v>
       </c>
@@ -13807,7 +13807,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>325</v>
       </c>
@@ -13830,7 +13830,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>325</v>
       </c>
@@ -13853,7 +13853,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>325</v>
       </c>
@@ -13876,7 +13876,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>182</v>
       </c>
@@ -13899,7 +13899,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>182</v>
       </c>
@@ -13922,7 +13922,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>182</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>182</v>
       </c>
@@ -13968,7 +13968,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -13991,7 +13991,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -14014,7 +14014,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -14037,7 +14037,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -14060,7 +14060,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -14083,7 +14083,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -14129,7 +14129,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>3</v>
       </c>
@@ -14152,7 +14152,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>3</v>
       </c>
@@ -14175,7 +14175,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>35</v>
       </c>
@@ -14198,7 +14198,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>35</v>
       </c>
@@ -14221,7 +14221,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>35</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>35</v>
       </c>
@@ -14267,7 +14267,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>35</v>
       </c>
@@ -14290,7 +14290,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>35</v>
       </c>
@@ -14313,7 +14313,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>35</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>35</v>
       </c>
@@ -14359,7 +14359,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>35</v>
       </c>
@@ -14382,7 +14382,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>41</v>
       </c>
@@ -14405,7 +14405,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>41</v>
       </c>
@@ -14428,7 +14428,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>41</v>
       </c>
@@ -14451,7 +14451,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>48</v>
       </c>
@@ -14474,7 +14474,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>48</v>
       </c>
@@ -14497,7 +14497,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>48</v>
       </c>
@@ -14520,7 +14520,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>24</v>
       </c>
@@ -14543,7 +14543,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>24</v>
       </c>
@@ -14566,7 +14566,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>11</v>
       </c>
@@ -14589,7 +14589,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>11</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>11</v>
       </c>
@@ -14635,7 +14635,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>11</v>
       </c>
@@ -14658,7 +14658,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>11</v>
       </c>
@@ -14681,7 +14681,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>11</v>
       </c>
@@ -14704,7 +14704,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>11</v>
       </c>
@@ -14727,7 +14727,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>11</v>
       </c>
@@ -14750,7 +14750,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>11</v>
       </c>
@@ -14773,7 +14773,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>15</v>
       </c>
@@ -14796,7 +14796,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>15</v>
       </c>
@@ -14819,7 +14819,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>15</v>
       </c>
@@ -14842,7 +14842,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>15</v>
       </c>
@@ -14865,7 +14865,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>15</v>
       </c>
@@ -14888,7 +14888,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>15</v>
       </c>
@@ -14911,7 +14911,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>15</v>
       </c>
@@ -14934,7 +14934,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>15</v>
       </c>
@@ -14957,7 +14957,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>15</v>
       </c>
@@ -14980,7 +14980,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>37</v>
       </c>
@@ -15003,7 +15003,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>37</v>
       </c>
@@ -15026,7 +15026,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>39</v>
       </c>
@@ -15049,7 +15049,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>39</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>39</v>
       </c>
@@ -15095,7 +15095,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A135" s="1" t="s">
         <v>39</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A136" s="1" t="s">
         <v>39</v>
       </c>
@@ -15157,19 +15157,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G134"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.1640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="25.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="77.33203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="81.1640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="81.1640625" style="28" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.1640625" style="28"/>
+    <col min="5" max="5" width="21.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="81.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="81.109375" style="28" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>187</v>
       </c>
@@ -15192,7 +15192,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>44</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>44</v>
       </c>
@@ -15238,7 +15238,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>130</v>
       </c>
@@ -15261,7 +15261,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>130</v>
       </c>
@@ -15284,7 +15284,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>130</v>
       </c>
@@ -15307,7 +15307,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>130</v>
       </c>
@@ -15330,7 +15330,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>59</v>
       </c>
@@ -15353,7 +15353,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
@@ -15376,7 +15376,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>59</v>
       </c>
@@ -15399,7 +15399,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>59</v>
       </c>
@@ -15422,7 +15422,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>59</v>
       </c>
@@ -15445,7 +15445,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>61</v>
       </c>
@@ -15468,7 +15468,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>61</v>
       </c>
@@ -15491,7 +15491,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
@@ -15514,7 +15514,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>17</v>
       </c>
@@ -15537,7 +15537,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>17</v>
       </c>
@@ -15560,7 +15560,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>17</v>
       </c>
@@ -15583,7 +15583,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -15606,7 +15606,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>17</v>
       </c>
@@ -15629,7 +15629,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>17</v>
       </c>
@@ -15652,7 +15652,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:7" ht="158.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>17</v>
       </c>
@@ -15675,7 +15675,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>19</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>19</v>
       </c>
@@ -15721,7 +15721,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>19</v>
       </c>
@@ -15744,7 +15744,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>19</v>
       </c>
@@ -15767,7 +15767,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>19</v>
       </c>
@@ -15790,7 +15790,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>19</v>
       </c>
@@ -15813,7 +15813,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>21</v>
       </c>
@@ -15836,7 +15836,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>56</v>
       </c>
@@ -15859,7 +15859,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>56</v>
       </c>
@@ -15882,7 +15882,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>56</v>
       </c>
@@ -15905,7 +15905,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>56</v>
       </c>
@@ -15928,7 +15928,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>69</v>
       </c>
@@ -15951,7 +15951,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>69</v>
       </c>
@@ -15974,7 +15974,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>69</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>71</v>
       </c>
@@ -16020,7 +16020,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>71</v>
       </c>
@@ -16043,7 +16043,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>71</v>
       </c>
@@ -16066,7 +16066,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>63</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>63</v>
       </c>
@@ -16112,7 +16112,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>63</v>
       </c>
@@ -16135,7 +16135,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>63</v>
       </c>
@@ -16158,7 +16158,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:7" ht="216" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>63</v>
       </c>
@@ -16181,7 +16181,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>66</v>
       </c>
@@ -16204,7 +16204,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>66</v>
       </c>
@@ -16227,7 +16227,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>66</v>
       </c>
@@ -16250,7 +16250,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:7" ht="288" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>66</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>73</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>73</v>
       </c>
@@ -16319,7 +16319,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>73</v>
       </c>
@@ -16342,7 +16342,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
@@ -16365,7 +16365,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>6</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>6</v>
       </c>
@@ -16411,7 +16411,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>6</v>
       </c>
@@ -16434,7 +16434,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>6</v>
       </c>
@@ -16457,7 +16457,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>6</v>
       </c>
@@ -16480,7 +16480,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>10</v>
       </c>
@@ -16503,7 +16503,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>10</v>
       </c>
@@ -16526,7 +16526,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>10</v>
       </c>
@@ -16549,7 +16549,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>10</v>
       </c>
@@ -16572,7 +16572,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>10</v>
       </c>
@@ -16595,7 +16595,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:7" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -16618,7 +16618,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>28</v>
       </c>
@@ -16641,7 +16641,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>28</v>
       </c>
@@ -16664,7 +16664,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>28</v>
       </c>
@@ -16687,7 +16687,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="176" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:7" ht="172.8" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>28</v>
       </c>
@@ -16710,7 +16710,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>31</v>
       </c>
@@ -16733,7 +16733,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>31</v>
       </c>
@@ -16756,7 +16756,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>31</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="224" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>31</v>
       </c>
@@ -16802,7 +16802,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>51</v>
       </c>
@@ -16825,7 +16825,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>51</v>
       </c>
@@ -16848,7 +16848,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>51</v>
       </c>
@@ -16871,7 +16871,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>51</v>
       </c>
@@ -16894,7 +16894,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>325</v>
       </c>
@@ -16917,7 +16917,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>325</v>
       </c>
@@ -16940,7 +16940,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>325</v>
       </c>
@@ -16963,7 +16963,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="256" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>325</v>
       </c>
@@ -16986,7 +16986,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>182</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A81" s="1" t="s">
         <v>182</v>
       </c>
@@ -17032,7 +17032,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A82" s="1" t="s">
         <v>182</v>
       </c>
@@ -17055,7 +17055,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="320" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:7" ht="331.2" x14ac:dyDescent="0.3">
       <c r="A83" s="1" t="s">
         <v>182</v>
       </c>
@@ -17078,7 +17078,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A84" s="1" t="s">
         <v>3</v>
       </c>
@@ -17101,7 +17101,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A85" s="1" t="s">
         <v>3</v>
       </c>
@@ -17124,7 +17124,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A86" s="1" t="s">
         <v>3</v>
       </c>
@@ -17147,7 +17147,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A87" s="1" t="s">
         <v>3</v>
       </c>
@@ -17170,7 +17170,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A88" s="1" t="s">
         <v>3</v>
       </c>
@@ -17193,7 +17193,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A89" s="1" t="s">
         <v>3</v>
       </c>
@@ -17216,7 +17216,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A90" s="1" t="s">
         <v>3</v>
       </c>
@@ -17239,7 +17239,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A91" s="1" t="s">
         <v>3</v>
       </c>
@@ -17262,7 +17262,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="350" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:7" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A92" s="1" t="s">
         <v>3</v>
       </c>
@@ -17285,7 +17285,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A93" s="1" t="s">
         <v>35</v>
       </c>
@@ -17308,7 +17308,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A94" s="1" t="s">
         <v>35</v>
       </c>
@@ -17331,7 +17331,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A95" s="1" t="s">
         <v>35</v>
       </c>
@@ -17354,7 +17354,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A96" s="1" t="s">
         <v>35</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A97" s="1" t="s">
         <v>35</v>
       </c>
@@ -17400,7 +17400,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="98" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A98" s="1" t="s">
         <v>35</v>
       </c>
@@ -17423,7 +17423,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A99" s="1" t="s">
         <v>35</v>
       </c>
@@ -17446,7 +17446,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A100" s="1" t="s">
         <v>35</v>
       </c>
@@ -17469,7 +17469,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A101" s="1" t="s">
         <v>35</v>
       </c>
@@ -17492,7 +17492,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="102" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A102" s="1" t="s">
         <v>41</v>
       </c>
@@ -17515,7 +17515,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="103" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A103" s="1" t="s">
         <v>41</v>
       </c>
@@ -17538,7 +17538,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="304" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:7" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A104" s="1" t="s">
         <v>41</v>
       </c>
@@ -17561,7 +17561,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A105" s="1" t="s">
         <v>48</v>
       </c>
@@ -17584,7 +17584,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A106" s="1" t="s">
         <v>48</v>
       </c>
@@ -17607,7 +17607,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="288" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:7" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A107" s="1" t="s">
         <v>48</v>
       </c>
@@ -17630,7 +17630,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A108" s="1" t="s">
         <v>24</v>
       </c>
@@ -17653,7 +17653,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="192" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A109" s="1" t="s">
         <v>24</v>
       </c>
@@ -17676,7 +17676,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A110" s="1" t="s">
         <v>11</v>
       </c>
@@ -17699,7 +17699,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A111" s="1" t="s">
         <v>11</v>
       </c>
@@ -17722,7 +17722,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A112" s="1" t="s">
         <v>11</v>
       </c>
@@ -17745,7 +17745,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A113" s="1" t="s">
         <v>11</v>
       </c>
@@ -17768,7 +17768,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A114" s="1" t="s">
         <v>11</v>
       </c>
@@ -17791,7 +17791,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A115" s="1" t="s">
         <v>11</v>
       </c>
@@ -17814,7 +17814,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A116" s="1" t="s">
         <v>11</v>
       </c>
@@ -17837,7 +17837,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A117" s="1" t="s">
         <v>11</v>
       </c>
@@ -17860,7 +17860,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="272" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:7" ht="259.2" x14ac:dyDescent="0.3">
       <c r="A118" s="1" t="s">
         <v>11</v>
       </c>
@@ -17883,7 +17883,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A119" s="1" t="s">
         <v>15</v>
       </c>
@@ -17906,7 +17906,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A120" s="1" t="s">
         <v>15</v>
       </c>
@@ -17929,7 +17929,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="121" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A121" s="1" t="s">
         <v>15</v>
       </c>
@@ -17952,7 +17952,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="122" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A122" s="1" t="s">
         <v>15</v>
       </c>
@@ -17975,7 +17975,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A123" s="1" t="s">
         <v>15</v>
       </c>
@@ -17998,7 +17998,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A124" s="1" t="s">
         <v>15</v>
       </c>
@@ -18021,7 +18021,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A125" s="1" t="s">
         <v>15</v>
       </c>
@@ -18044,7 +18044,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A126" s="1" t="s">
         <v>15</v>
       </c>
@@ -18067,7 +18067,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="208" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:7" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A127" s="1" t="s">
         <v>15</v>
       </c>
@@ -18090,7 +18090,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A128" s="1" t="s">
         <v>37</v>
       </c>
@@ -18113,7 +18113,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:7" ht="244.8" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>37</v>
       </c>
@@ -18136,7 +18136,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>39</v>
       </c>
@@ -18159,7 +18159,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>39</v>
       </c>
@@ -18182,7 +18182,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A132" s="1" t="s">
         <v>39</v>
       </c>
@@ -18205,7 +18205,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="133" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A133" s="1" t="s">
         <v>39</v>
       </c>
@@ -18228,7 +18228,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="240" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:7" ht="230.4" x14ac:dyDescent="0.3">
       <c r="A134" s="1" t="s">
         <v>39</v>
       </c>
@@ -18261,17 +18261,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{930E65A7-049E-4487-944F-9576DFD82A03}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="35.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="35.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.83203125" style="28" customWidth="1"/>
+    <col min="1" max="1" width="13.77734375" style="28" customWidth="1"/>
     <col min="2" max="2" width="47.6640625" style="28" customWidth="1"/>
     <col min="3" max="3" width="62.33203125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="49.1640625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="49.109375" style="28" customWidth="1"/>
     <col min="5" max="5" width="30" style="28" customWidth="1"/>
-    <col min="6" max="16384" width="35.1640625" style="28"/>
+    <col min="6" max="16384" width="35.109375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="39" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" s="39" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="38" t="s">
         <v>187</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="144" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>17</v>
       </c>
@@ -18311,7 +18311,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="144" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>51</v>
       </c>
@@ -18331,7 +18331,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="128" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>73</v>
       </c>
@@ -18351,7 +18351,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="128" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>56</v>
       </c>
@@ -18371,7 +18371,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="112" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>63</v>
       </c>
@@ -18391,7 +18391,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="144" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" ht="144" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>66</v>
       </c>
@@ -18419,15 +18419,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56314C74-21F4-423D-BAB3-8F17C1A7DE0C}">
   <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" style="43" customWidth="1"/>
     <col min="2" max="4" width="57.6640625" style="43" customWidth="1"/>
     <col min="5" max="5" width="46" style="43" customWidth="1"/>
-    <col min="6" max="16384" width="9.1640625" style="43"/>
+    <col min="6" max="16384" width="9.109375" style="43"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="1" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="47" t="s">
         <v>187</v>
       </c>
@@ -18444,7 +18444,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="128" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A2" s="45" t="s">
         <v>63</v>
       </c>
@@ -18461,7 +18461,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="128" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A3" s="50" t="s">
         <v>66</v>
       </c>
@@ -18493,20 +18493,20 @@
     <tabColor theme="6"/>
   </sheetPr>
   <dimension ref="A1:H30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="63.1640625" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="63.109375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="54.83203125" style="6" customWidth="1"/>
-    <col min="3" max="3" width="60.5" style="6" customWidth="1"/>
-    <col min="4" max="4" width="60.5" style="7" customWidth="1"/>
-    <col min="5" max="5" width="20.5" style="10" customWidth="1"/>
-    <col min="6" max="6" width="26.83203125" style="10" customWidth="1"/>
+    <col min="2" max="2" width="54.77734375" style="6" customWidth="1"/>
+    <col min="3" max="3" width="60.44140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="60.44140625" style="7" customWidth="1"/>
+    <col min="5" max="5" width="20.44140625" style="10" customWidth="1"/>
+    <col min="6" max="6" width="26.77734375" style="10" customWidth="1"/>
     <col min="7" max="7" width="23" style="10" customWidth="1"/>
     <col min="8" max="8" width="54" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="63.1640625" style="6"/>
+    <col min="9" max="16384" width="63.109375" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="27" customFormat="1" ht="30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="27" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="23" t="s">
         <v>187</v>
       </c>
@@ -18532,7 +18532,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="120" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="138" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>3</v>
       </c>
@@ -18558,7 +18558,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="150" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="165.6" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>6</v>
       </c>
@@ -18584,7 +18584,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>10</v>
       </c>
@@ -18610,7 +18610,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
@@ -18636,7 +18636,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>15</v>
       </c>
@@ -18662,7 +18662,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>17</v>
       </c>
@@ -18688,7 +18688,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>19</v>
       </c>
@@ -18714,7 +18714,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>21</v>
       </c>
@@ -18740,7 +18740,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>24</v>
       </c>
@@ -18766,7 +18766,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A11" s="12" t="s">
         <v>28</v>
       </c>
@@ -18792,7 +18792,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>31</v>
       </c>
@@ -18818,7 +18818,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="120" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A13" s="12" t="s">
         <v>182</v>
       </c>
@@ -18844,7 +18844,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>35</v>
       </c>
@@ -18870,7 +18870,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A15" s="12" t="s">
         <v>37</v>
       </c>
@@ -18896,7 +18896,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>39</v>
       </c>
@@ -18922,7 +18922,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="120" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A17" s="12" t="s">
         <v>41</v>
       </c>
@@ -18948,7 +18948,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>44</v>
       </c>
@@ -18974,7 +18974,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A19" s="12" t="s">
         <v>48</v>
       </c>
@@ -19000,7 +19000,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="120" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" ht="124.2" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>51</v>
       </c>
@@ -19026,7 +19026,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A21" s="12" t="s">
         <v>54</v>
       </c>
@@ -19052,7 +19052,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>56</v>
       </c>
@@ -19075,7 +19075,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A23" s="12" t="s">
         <v>130</v>
       </c>
@@ -19098,7 +19098,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>59</v>
       </c>
@@ -19121,7 +19121,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A25" s="12" t="s">
         <v>61</v>
       </c>
@@ -19144,7 +19144,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>63</v>
       </c>
@@ -19167,7 +19167,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A27" s="12" t="s">
         <v>73</v>
       </c>
@@ -19190,7 +19190,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="105" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="110.4" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>66</v>
       </c>
@@ -19213,7 +19213,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="90" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" ht="96.6" x14ac:dyDescent="0.3">
       <c r="A29" s="12" t="s">
         <v>69</v>
       </c>
@@ -19236,7 +19236,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="75" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A30" s="17" t="s">
         <v>71</v>
       </c>
